--- a/Datas/规划.xlsx
+++ b/Datas/规划.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>装备店</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -162,6 +162,30 @@
   </si>
   <si>
     <t>植物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兽皮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>皮革</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔兽毛皮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>皮革</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -487,13 +511,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:F16"/>
+  <dimension ref="B1:K16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="5" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C1" t="s">
         <v>15</v>
       </c>
@@ -501,7 +525,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -518,7 +542,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>2</v>
       </c>
@@ -535,7 +559,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -546,7 +570,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -554,7 +578,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>7</v>
       </c>
@@ -565,7 +589,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -576,38 +600,56 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="J8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="J9" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="J10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>14</v>
       </c>
@@ -618,17 +660,17 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>19</v>
       </c>
